--- a/đầu vào/tháng 7/TK 136 - HCM.xlsx
+++ b/đầu vào/tháng 7/TK 136 - HCM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA\DATA KTTH\KIEMDO_136-336\đầu vào\tháng 7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC9425E9-03C6-404F-9919-00FA2918B4CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFF4B216-5869-488B-A3FC-C885D217B303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12185,7 +12185,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="42">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -12407,6 +12407,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="18">
     <border>
@@ -12667,7 +12679,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -12751,6 +12763,15 @@
     <xf numFmtId="164" fontId="20" fillId="37" borderId="12" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="20" fillId="38" borderId="12" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="39" borderId="12" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
@@ -12760,6 +12781,27 @@
     <xf numFmtId="0" fontId="21" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="34" borderId="10" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="34" borderId="16" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -12767,12 +12809,6 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="34" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12784,28 +12820,10 @@
     <xf numFmtId="0" fontId="21" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="34" borderId="10" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="34" borderId="16" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="38" borderId="12" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="20" fillId="40" borderId="12" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="39" borderId="12" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="20" fillId="41" borderId="12" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -13181,19 +13199,19 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
+      <c r="B1" s="42"/>
     </row>
     <row r="2" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="32"/>
+      <c r="B2" s="42"/>
     </row>
     <row r="3" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="32"/>
+      <c r="B3" s="42"/>
     </row>
     <row r="4" spans="1:9" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
@@ -13202,42 +13220,42 @@
       <c r="B4" s="1"/>
     </row>
     <row r="5" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="33" t="s">
+      <c r="A5" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="33"/>
+      <c r="B5" s="43"/>
     </row>
     <row r="6" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="34"/>
+      <c r="B6" s="44"/>
     </row>
     <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="34" t="s">
+      <c r="A7" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="34"/>
+      <c r="B7" s="44"/>
     </row>
     <row r="9" spans="1:9" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="35" t="s">
+      <c r="A9" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="37" t="s">
+      <c r="B9" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="38"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="35" t="s">
+      <c r="C9" s="46"/>
+      <c r="D9" s="47"/>
+      <c r="E9" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="40" t="s">
+      <c r="F9" s="38" t="s">
         <v>1151</v>
       </c>
-      <c r="G9" s="40" t="s">
+      <c r="G9" s="38" t="s">
         <v>1152</v>
       </c>
-      <c r="H9" s="35" t="s">
+      <c r="H9" s="40" t="s">
         <v>10</v>
       </c>
       <c r="I9" s="4" t="s">
@@ -13245,7 +13263,7 @@
       </c>
     </row>
     <row r="10" spans="1:9" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="36"/>
+      <c r="A10" s="41"/>
       <c r="B10" s="6" t="s">
         <v>12</v>
       </c>
@@ -13255,35 +13273,35 @@
       <c r="D10" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="36"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="36"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="41"/>
       <c r="I10" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="42" t="s">
+      <c r="A11" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="43"/>
-      <c r="C11" s="43"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="43"/>
-      <c r="G11" s="43"/>
-      <c r="H11" s="43"/>
-      <c r="I11" s="44"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="36"/>
+      <c r="H11" s="36"/>
+      <c r="I11" s="37"/>
     </row>
     <row r="12" spans="1:9" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="29" t="s">
+      <c r="A12" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="30"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="31"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="34"/>
       <c r="F12" s="22">
         <v>412717361000</v>
       </c>
@@ -31652,13 +31670,13 @@
       </c>
     </row>
     <row r="693" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A693" s="29" t="s">
+      <c r="A693" s="32" t="s">
         <v>964</v>
       </c>
-      <c r="B693" s="30"/>
-      <c r="C693" s="30"/>
-      <c r="D693" s="30"/>
-      <c r="E693" s="31"/>
+      <c r="B693" s="33"/>
+      <c r="C693" s="33"/>
+      <c r="D693" s="33"/>
+      <c r="E693" s="34"/>
       <c r="F693" s="22">
         <v>103403498084</v>
       </c>
@@ -31669,13 +31687,13 @@
       <c r="I693" s="11"/>
     </row>
     <row r="694" spans="1:9" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A694" s="29" t="s">
+      <c r="A694" s="32" t="s">
         <v>965</v>
       </c>
-      <c r="B694" s="30"/>
-      <c r="C694" s="30"/>
-      <c r="D694" s="30"/>
-      <c r="E694" s="31"/>
+      <c r="B694" s="33"/>
+      <c r="C694" s="33"/>
+      <c r="D694" s="33"/>
+      <c r="E694" s="34"/>
       <c r="F694" s="23"/>
       <c r="G694" s="22">
         <v>926272738075</v>
@@ -31684,26 +31702,26 @@
       <c r="I694" s="11"/>
     </row>
     <row r="695" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A695" s="42" t="s">
+      <c r="A695" s="35" t="s">
         <v>966</v>
       </c>
-      <c r="B695" s="43"/>
-      <c r="C695" s="43"/>
-      <c r="D695" s="43"/>
-      <c r="E695" s="43"/>
-      <c r="F695" s="43"/>
-      <c r="G695" s="43"/>
-      <c r="H695" s="43"/>
-      <c r="I695" s="44"/>
+      <c r="B695" s="36"/>
+      <c r="C695" s="36"/>
+      <c r="D695" s="36"/>
+      <c r="E695" s="36"/>
+      <c r="F695" s="36"/>
+      <c r="G695" s="36"/>
+      <c r="H695" s="36"/>
+      <c r="I695" s="37"/>
     </row>
     <row r="696" spans="1:9" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A696" s="29" t="s">
+      <c r="A696" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B696" s="30"/>
-      <c r="C696" s="30"/>
-      <c r="D696" s="30"/>
-      <c r="E696" s="31"/>
+      <c r="B696" s="33"/>
+      <c r="C696" s="33"/>
+      <c r="D696" s="33"/>
+      <c r="E696" s="34"/>
       <c r="F696" s="23"/>
       <c r="G696" s="22">
         <v>3844085208</v>
@@ -34547,13 +34565,13 @@
       </c>
     </row>
     <row r="802" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A802" s="29" t="s">
+      <c r="A802" s="32" t="s">
         <v>964</v>
       </c>
-      <c r="B802" s="30"/>
-      <c r="C802" s="30"/>
-      <c r="D802" s="30"/>
-      <c r="E802" s="31"/>
+      <c r="B802" s="33"/>
+      <c r="C802" s="33"/>
+      <c r="D802" s="33"/>
+      <c r="E802" s="34"/>
       <c r="F802" s="22">
         <v>56850487</v>
       </c>
@@ -34564,13 +34582,13 @@
       <c r="I802" s="11"/>
     </row>
     <row r="803" spans="1:9" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A803" s="29" t="s">
+      <c r="A803" s="32" t="s">
         <v>965</v>
       </c>
-      <c r="B803" s="30"/>
-      <c r="C803" s="30"/>
-      <c r="D803" s="30"/>
-      <c r="E803" s="31"/>
+      <c r="B803" s="33"/>
+      <c r="C803" s="33"/>
+      <c r="D803" s="33"/>
+      <c r="E803" s="34"/>
       <c r="F803" s="23"/>
       <c r="G803" s="22">
         <v>4510359049</v>
@@ -34579,26 +34597,26 @@
       <c r="I803" s="11"/>
     </row>
     <row r="804" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A804" s="42" t="s">
+      <c r="A804" s="35" t="s">
         <v>1055</v>
       </c>
-      <c r="B804" s="43"/>
-      <c r="C804" s="43"/>
-      <c r="D804" s="43"/>
-      <c r="E804" s="43"/>
-      <c r="F804" s="43"/>
-      <c r="G804" s="43"/>
-      <c r="H804" s="43"/>
-      <c r="I804" s="44"/>
+      <c r="B804" s="36"/>
+      <c r="C804" s="36"/>
+      <c r="D804" s="36"/>
+      <c r="E804" s="36"/>
+      <c r="F804" s="36"/>
+      <c r="G804" s="36"/>
+      <c r="H804" s="36"/>
+      <c r="I804" s="37"/>
     </row>
     <row r="805" spans="1:9" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A805" s="29" t="s">
+      <c r="A805" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B805" s="30"/>
-      <c r="C805" s="30"/>
-      <c r="D805" s="30"/>
-      <c r="E805" s="31"/>
+      <c r="B805" s="33"/>
+      <c r="C805" s="33"/>
+      <c r="D805" s="33"/>
+      <c r="E805" s="34"/>
       <c r="F805" s="22">
         <v>9983257640</v>
       </c>
@@ -34688,13 +34706,13 @@
       </c>
     </row>
     <row r="809" spans="1:9" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A809" s="29" t="s">
+      <c r="A809" s="32" t="s">
         <v>964</v>
       </c>
-      <c r="B809" s="30"/>
-      <c r="C809" s="30"/>
-      <c r="D809" s="30"/>
-      <c r="E809" s="31"/>
+      <c r="B809" s="33"/>
+      <c r="C809" s="33"/>
+      <c r="D809" s="33"/>
+      <c r="E809" s="34"/>
       <c r="F809" s="23"/>
       <c r="G809" s="22">
         <v>3492258688</v>
@@ -34703,13 +34721,13 @@
       <c r="I809" s="11"/>
     </row>
     <row r="810" spans="1:9" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A810" s="29" t="s">
+      <c r="A810" s="32" t="s">
         <v>965</v>
       </c>
-      <c r="B810" s="30"/>
-      <c r="C810" s="30"/>
-      <c r="D810" s="30"/>
-      <c r="E810" s="31"/>
+      <c r="B810" s="33"/>
+      <c r="C810" s="33"/>
+      <c r="D810" s="33"/>
+      <c r="E810" s="34"/>
       <c r="F810" s="22">
         <v>6490998952</v>
       </c>
@@ -34718,26 +34736,26 @@
       <c r="I810" s="11"/>
     </row>
     <row r="811" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A811" s="42" t="s">
+      <c r="A811" s="35" t="s">
         <v>1063</v>
       </c>
-      <c r="B811" s="43"/>
-      <c r="C811" s="43"/>
-      <c r="D811" s="43"/>
-      <c r="E811" s="43"/>
-      <c r="F811" s="43"/>
-      <c r="G811" s="43"/>
-      <c r="H811" s="43"/>
-      <c r="I811" s="44"/>
+      <c r="B811" s="36"/>
+      <c r="C811" s="36"/>
+      <c r="D811" s="36"/>
+      <c r="E811" s="36"/>
+      <c r="F811" s="36"/>
+      <c r="G811" s="36"/>
+      <c r="H811" s="36"/>
+      <c r="I811" s="37"/>
     </row>
     <row r="812" spans="1:9" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A812" s="29" t="s">
+      <c r="A812" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B812" s="30"/>
-      <c r="C812" s="30"/>
-      <c r="D812" s="30"/>
-      <c r="E812" s="31"/>
+      <c r="B812" s="33"/>
+      <c r="C812" s="33"/>
+      <c r="D812" s="33"/>
+      <c r="E812" s="34"/>
       <c r="F812" s="23"/>
       <c r="G812" s="22">
         <v>389211761633</v>
@@ -35016,13 +35034,13 @@
       </c>
     </row>
     <row r="823" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A823" s="29" t="s">
+      <c r="A823" s="32" t="s">
         <v>964</v>
       </c>
-      <c r="B823" s="30"/>
-      <c r="C823" s="30"/>
-      <c r="D823" s="30"/>
-      <c r="E823" s="31"/>
+      <c r="B823" s="33"/>
+      <c r="C823" s="33"/>
+      <c r="D823" s="33"/>
+      <c r="E823" s="34"/>
       <c r="F823" s="22">
         <v>65497263619</v>
       </c>
@@ -35033,13 +35051,13 @@
       <c r="I823" s="11"/>
     </row>
     <row r="824" spans="1:9" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A824" s="29" t="s">
+      <c r="A824" s="32" t="s">
         <v>965</v>
       </c>
-      <c r="B824" s="30"/>
-      <c r="C824" s="30"/>
-      <c r="D824" s="30"/>
-      <c r="E824" s="31"/>
+      <c r="B824" s="33"/>
+      <c r="C824" s="33"/>
+      <c r="D824" s="33"/>
+      <c r="E824" s="34"/>
       <c r="F824" s="23"/>
       <c r="G824" s="22">
         <v>332768778610</v>
@@ -35048,26 +35066,26 @@
       <c r="I824" s="11"/>
     </row>
     <row r="825" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A825" s="42" t="s">
+      <c r="A825" s="35" t="s">
         <v>1085</v>
       </c>
-      <c r="B825" s="43"/>
-      <c r="C825" s="43"/>
-      <c r="D825" s="43"/>
-      <c r="E825" s="43"/>
-      <c r="F825" s="43"/>
-      <c r="G825" s="43"/>
-      <c r="H825" s="43"/>
-      <c r="I825" s="44"/>
+      <c r="B825" s="36"/>
+      <c r="C825" s="36"/>
+      <c r="D825" s="36"/>
+      <c r="E825" s="36"/>
+      <c r="F825" s="36"/>
+      <c r="G825" s="36"/>
+      <c r="H825" s="36"/>
+      <c r="I825" s="37"/>
     </row>
     <row r="826" spans="1:9" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A826" s="29" t="s">
+      <c r="A826" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B826" s="30"/>
-      <c r="C826" s="30"/>
-      <c r="D826" s="30"/>
-      <c r="E826" s="31"/>
+      <c r="B826" s="33"/>
+      <c r="C826" s="33"/>
+      <c r="D826" s="33"/>
+      <c r="E826" s="34"/>
       <c r="F826" s="23"/>
       <c r="G826" s="22">
         <v>514877839117</v>
@@ -35103,13 +35121,13 @@
       </c>
     </row>
     <row r="828" spans="1:9" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A828" s="29" t="s">
+      <c r="A828" s="32" t="s">
         <v>964</v>
       </c>
-      <c r="B828" s="30"/>
-      <c r="C828" s="30"/>
-      <c r="D828" s="30"/>
-      <c r="E828" s="31"/>
+      <c r="B828" s="33"/>
+      <c r="C828" s="33"/>
+      <c r="D828" s="33"/>
+      <c r="E828" s="34"/>
       <c r="F828" s="23"/>
       <c r="G828" s="22">
         <v>6501103895</v>
@@ -35118,13 +35136,13 @@
       <c r="I828" s="11"/>
     </row>
     <row r="829" spans="1:9" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A829" s="29" t="s">
+      <c r="A829" s="32" t="s">
         <v>965</v>
       </c>
-      <c r="B829" s="30"/>
-      <c r="C829" s="30"/>
-      <c r="D829" s="30"/>
-      <c r="E829" s="31"/>
+      <c r="B829" s="33"/>
+      <c r="C829" s="33"/>
+      <c r="D829" s="33"/>
+      <c r="E829" s="34"/>
       <c r="F829" s="23"/>
       <c r="G829" s="22">
         <v>521378943012</v>
@@ -35133,26 +35151,26 @@
       <c r="I829" s="11"/>
     </row>
     <row r="830" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A830" s="42" t="s">
+      <c r="A830" s="35" t="s">
         <v>1087</v>
       </c>
-      <c r="B830" s="43"/>
-      <c r="C830" s="43"/>
-      <c r="D830" s="43"/>
-      <c r="E830" s="43"/>
-      <c r="F830" s="43"/>
-      <c r="G830" s="43"/>
-      <c r="H830" s="43"/>
-      <c r="I830" s="44"/>
+      <c r="B830" s="36"/>
+      <c r="C830" s="36"/>
+      <c r="D830" s="36"/>
+      <c r="E830" s="36"/>
+      <c r="F830" s="36"/>
+      <c r="G830" s="36"/>
+      <c r="H830" s="36"/>
+      <c r="I830" s="37"/>
     </row>
     <row r="831" spans="1:9" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A831" s="29" t="s">
+      <c r="A831" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B831" s="30"/>
-      <c r="C831" s="30"/>
-      <c r="D831" s="30"/>
-      <c r="E831" s="31"/>
+      <c r="B831" s="33"/>
+      <c r="C831" s="33"/>
+      <c r="D831" s="33"/>
+      <c r="E831" s="34"/>
       <c r="F831" s="23"/>
       <c r="G831" s="22">
         <v>16506012261</v>
@@ -35161,26 +35179,26 @@
       <c r="I831" s="11"/>
     </row>
     <row r="832" spans="1:9" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A832" s="29" t="s">
+      <c r="A832" s="32" t="s">
         <v>964</v>
       </c>
-      <c r="B832" s="30"/>
-      <c r="C832" s="30"/>
-      <c r="D832" s="30"/>
-      <c r="E832" s="31"/>
+      <c r="B832" s="33"/>
+      <c r="C832" s="33"/>
+      <c r="D832" s="33"/>
+      <c r="E832" s="34"/>
       <c r="F832" s="23"/>
       <c r="G832" s="23"/>
       <c r="H832" s="10"/>
       <c r="I832" s="11"/>
     </row>
     <row r="833" spans="1:9" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A833" s="29" t="s">
+      <c r="A833" s="32" t="s">
         <v>965</v>
       </c>
-      <c r="B833" s="30"/>
-      <c r="C833" s="30"/>
-      <c r="D833" s="30"/>
-      <c r="E833" s="31"/>
+      <c r="B833" s="33"/>
+      <c r="C833" s="33"/>
+      <c r="D833" s="33"/>
+      <c r="E833" s="34"/>
       <c r="F833" s="23"/>
       <c r="G833" s="22">
         <v>16506012261</v>
@@ -35189,26 +35207,26 @@
       <c r="I833" s="11"/>
     </row>
     <row r="834" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A834" s="42" t="s">
+      <c r="A834" s="35" t="s">
         <v>1088</v>
       </c>
-      <c r="B834" s="43"/>
-      <c r="C834" s="43"/>
-      <c r="D834" s="43"/>
-      <c r="E834" s="43"/>
-      <c r="F834" s="43"/>
-      <c r="G834" s="43"/>
-      <c r="H834" s="43"/>
-      <c r="I834" s="44"/>
+      <c r="B834" s="36"/>
+      <c r="C834" s="36"/>
+      <c r="D834" s="36"/>
+      <c r="E834" s="36"/>
+      <c r="F834" s="36"/>
+      <c r="G834" s="36"/>
+      <c r="H834" s="36"/>
+      <c r="I834" s="37"/>
     </row>
     <row r="835" spans="1:9" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A835" s="29" t="s">
+      <c r="A835" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B835" s="30"/>
-      <c r="C835" s="30"/>
-      <c r="D835" s="30"/>
-      <c r="E835" s="31"/>
+      <c r="B835" s="33"/>
+      <c r="C835" s="33"/>
+      <c r="D835" s="33"/>
+      <c r="E835" s="34"/>
       <c r="F835" s="23"/>
       <c r="G835" s="23"/>
       <c r="H835" s="10"/>
@@ -35269,13 +35287,13 @@
       </c>
     </row>
     <row r="838" spans="1:9" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A838" s="29" t="s">
+      <c r="A838" s="32" t="s">
         <v>964</v>
       </c>
-      <c r="B838" s="30"/>
-      <c r="C838" s="30"/>
-      <c r="D838" s="30"/>
-      <c r="E838" s="31"/>
+      <c r="B838" s="33"/>
+      <c r="C838" s="33"/>
+      <c r="D838" s="33"/>
+      <c r="E838" s="34"/>
       <c r="F838" s="22">
         <v>15555384491</v>
       </c>
@@ -35284,13 +35302,13 @@
       <c r="I838" s="11"/>
     </row>
     <row r="839" spans="1:9" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A839" s="29" t="s">
+      <c r="A839" s="32" t="s">
         <v>965</v>
       </c>
-      <c r="B839" s="30"/>
-      <c r="C839" s="30"/>
-      <c r="D839" s="30"/>
-      <c r="E839" s="31"/>
+      <c r="B839" s="33"/>
+      <c r="C839" s="33"/>
+      <c r="D839" s="33"/>
+      <c r="E839" s="34"/>
       <c r="F839" s="22">
         <v>15555384491</v>
       </c>
@@ -35299,26 +35317,26 @@
       <c r="I839" s="11"/>
     </row>
     <row r="840" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A840" s="42" t="s">
+      <c r="A840" s="35" t="s">
         <v>1089</v>
       </c>
-      <c r="B840" s="43"/>
-      <c r="C840" s="43"/>
-      <c r="D840" s="43"/>
-      <c r="E840" s="43"/>
-      <c r="F840" s="43"/>
-      <c r="G840" s="43"/>
-      <c r="H840" s="43"/>
-      <c r="I840" s="44"/>
+      <c r="B840" s="36"/>
+      <c r="C840" s="36"/>
+      <c r="D840" s="36"/>
+      <c r="E840" s="36"/>
+      <c r="F840" s="36"/>
+      <c r="G840" s="36"/>
+      <c r="H840" s="36"/>
+      <c r="I840" s="37"/>
     </row>
     <row r="841" spans="1:9" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A841" s="29" t="s">
+      <c r="A841" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B841" s="30"/>
-      <c r="C841" s="30"/>
-      <c r="D841" s="30"/>
-      <c r="E841" s="31"/>
+      <c r="B841" s="33"/>
+      <c r="C841" s="33"/>
+      <c r="D841" s="33"/>
+      <c r="E841" s="34"/>
       <c r="F841" s="22">
         <v>342749567830</v>
       </c>
@@ -35369,7 +35387,7 @@
       <c r="E843" s="15" t="s">
         <v>1113</v>
       </c>
-      <c r="F843" s="25">
+      <c r="F843" s="49">
         <v>1320517500</v>
       </c>
       <c r="G843" s="24"/>
@@ -35396,7 +35414,7 @@
       <c r="E844" s="15" t="s">
         <v>1115</v>
       </c>
-      <c r="F844" s="25">
+      <c r="F844" s="49">
         <v>729000000</v>
       </c>
       <c r="G844" s="24"/>
@@ -35423,7 +35441,7 @@
       <c r="E845" s="15" t="s">
         <v>1116</v>
       </c>
-      <c r="F845" s="25">
+      <c r="F845" s="49">
         <v>1075800000</v>
       </c>
       <c r="G845" s="24"/>
@@ -35451,7 +35469,7 @@
         <v>1117</v>
       </c>
       <c r="F846" s="24"/>
-      <c r="G846" s="25">
+      <c r="G846" s="48">
         <v>4274472878</v>
       </c>
       <c r="H846" s="15" t="s">
@@ -35558,7 +35576,7 @@
       <c r="E850" s="15" t="s">
         <v>1093</v>
       </c>
-      <c r="F850" s="46">
+      <c r="F850" s="29">
         <v>1963917778</v>
       </c>
       <c r="G850" s="24"/>
@@ -35585,7 +35603,7 @@
       <c r="E851" s="15" t="s">
         <v>1096</v>
       </c>
-      <c r="F851" s="46">
+      <c r="F851" s="29">
         <v>3951311154</v>
       </c>
       <c r="G851" s="24"/>
@@ -35639,7 +35657,7 @@
       <c r="E853" s="15" t="s">
         <v>1102</v>
       </c>
-      <c r="F853" s="46">
+      <c r="F853" s="29">
         <v>3451399200</v>
       </c>
       <c r="G853" s="24"/>
@@ -35693,7 +35711,7 @@
       <c r="E855" s="15" t="s">
         <v>1106</v>
       </c>
-      <c r="F855" s="46">
+      <c r="F855" s="29">
         <v>3589537560</v>
       </c>
       <c r="G855" s="24"/>
@@ -35801,7 +35819,7 @@
       <c r="E859" s="15" t="s">
         <v>1100</v>
       </c>
-      <c r="F859" s="47">
+      <c r="F859" s="30">
         <v>47879803</v>
       </c>
       <c r="G859" s="24"/>
@@ -35828,7 +35846,7 @@
       <c r="E860" s="15" t="s">
         <v>1078</v>
       </c>
-      <c r="F860" s="47">
+      <c r="F860" s="30">
         <v>6277098679</v>
       </c>
       <c r="G860" s="24"/>
@@ -35840,13 +35858,13 @@
       </c>
     </row>
     <row r="861" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A861" s="29" t="s">
+      <c r="A861" s="32" t="s">
         <v>964</v>
       </c>
-      <c r="B861" s="30"/>
-      <c r="C861" s="30"/>
-      <c r="D861" s="30"/>
-      <c r="E861" s="31"/>
+      <c r="B861" s="33"/>
+      <c r="C861" s="33"/>
+      <c r="D861" s="33"/>
+      <c r="E861" s="34"/>
       <c r="F861" s="22">
         <v>1381951681810</v>
       </c>
@@ -35857,13 +35875,13 @@
       <c r="I861" s="11"/>
     </row>
     <row r="862" spans="1:9" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A862" s="29" t="s">
+      <c r="A862" s="32" t="s">
         <v>965</v>
       </c>
-      <c r="B862" s="30"/>
-      <c r="C862" s="30"/>
-      <c r="D862" s="30"/>
-      <c r="E862" s="31"/>
+      <c r="B862" s="33"/>
+      <c r="C862" s="33"/>
+      <c r="D862" s="33"/>
+      <c r="E862" s="34"/>
       <c r="F862" s="22">
         <v>1615521348756</v>
       </c>
@@ -35872,26 +35890,26 @@
       <c r="I862" s="11"/>
     </row>
     <row r="863" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A863" s="42" t="s">
+      <c r="A863" s="35" t="s">
         <v>1120</v>
       </c>
-      <c r="B863" s="43"/>
-      <c r="C863" s="43"/>
-      <c r="D863" s="43"/>
-      <c r="E863" s="43"/>
-      <c r="F863" s="43"/>
-      <c r="G863" s="43"/>
-      <c r="H863" s="43"/>
-      <c r="I863" s="44"/>
+      <c r="B863" s="36"/>
+      <c r="C863" s="36"/>
+      <c r="D863" s="36"/>
+      <c r="E863" s="36"/>
+      <c r="F863" s="36"/>
+      <c r="G863" s="36"/>
+      <c r="H863" s="36"/>
+      <c r="I863" s="37"/>
     </row>
     <row r="864" spans="1:9" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A864" s="29" t="s">
+      <c r="A864" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B864" s="30"/>
-      <c r="C864" s="30"/>
-      <c r="D864" s="30"/>
-      <c r="E864" s="31"/>
+      <c r="B864" s="33"/>
+      <c r="C864" s="33"/>
+      <c r="D864" s="33"/>
+      <c r="E864" s="34"/>
       <c r="F864" s="22">
         <v>2076322697</v>
       </c>
@@ -35954,13 +35972,13 @@
       </c>
     </row>
     <row r="867" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A867" s="29" t="s">
+      <c r="A867" s="32" t="s">
         <v>964</v>
       </c>
-      <c r="B867" s="30"/>
-      <c r="C867" s="30"/>
-      <c r="D867" s="30"/>
-      <c r="E867" s="31"/>
+      <c r="B867" s="33"/>
+      <c r="C867" s="33"/>
+      <c r="D867" s="33"/>
+      <c r="E867" s="34"/>
       <c r="F867" s="22">
         <v>1937832476</v>
       </c>
@@ -35971,13 +35989,13 @@
       <c r="I867" s="11"/>
     </row>
     <row r="868" spans="1:9" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A868" s="29" t="s">
+      <c r="A868" s="32" t="s">
         <v>965</v>
       </c>
-      <c r="B868" s="30"/>
-      <c r="C868" s="30"/>
-      <c r="D868" s="30"/>
-      <c r="E868" s="31"/>
+      <c r="B868" s="33"/>
+      <c r="C868" s="33"/>
+      <c r="D868" s="33"/>
+      <c r="E868" s="34"/>
       <c r="F868" s="22">
         <v>1937832476</v>
       </c>
@@ -35986,26 +36004,26 @@
       <c r="I868" s="11"/>
     </row>
     <row r="869" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A869" s="42" t="s">
+      <c r="A869" s="35" t="s">
         <v>1121</v>
       </c>
-      <c r="B869" s="43"/>
-      <c r="C869" s="43"/>
-      <c r="D869" s="43"/>
-      <c r="E869" s="43"/>
-      <c r="F869" s="43"/>
-      <c r="G869" s="43"/>
-      <c r="H869" s="43"/>
-      <c r="I869" s="44"/>
+      <c r="B869" s="36"/>
+      <c r="C869" s="36"/>
+      <c r="D869" s="36"/>
+      <c r="E869" s="36"/>
+      <c r="F869" s="36"/>
+      <c r="G869" s="36"/>
+      <c r="H869" s="36"/>
+      <c r="I869" s="37"/>
     </row>
     <row r="870" spans="1:9" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A870" s="29" t="s">
+      <c r="A870" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B870" s="30"/>
-      <c r="C870" s="30"/>
-      <c r="D870" s="30"/>
-      <c r="E870" s="31"/>
+      <c r="B870" s="33"/>
+      <c r="C870" s="33"/>
+      <c r="D870" s="33"/>
+      <c r="E870" s="34"/>
       <c r="F870" s="22">
         <v>6263649174</v>
       </c>
@@ -36176,13 +36194,13 @@
       </c>
     </row>
     <row r="877" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A877" s="29" t="s">
+      <c r="A877" s="32" t="s">
         <v>964</v>
       </c>
-      <c r="B877" s="30"/>
-      <c r="C877" s="30"/>
-      <c r="D877" s="30"/>
-      <c r="E877" s="31"/>
+      <c r="B877" s="33"/>
+      <c r="C877" s="33"/>
+      <c r="D877" s="33"/>
+      <c r="E877" s="34"/>
       <c r="F877" s="22">
         <v>523006926</v>
       </c>
@@ -36193,13 +36211,13 @@
       <c r="I877" s="11"/>
     </row>
     <row r="878" spans="1:9" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A878" s="29" t="s">
+      <c r="A878" s="32" t="s">
         <v>965</v>
       </c>
-      <c r="B878" s="30"/>
-      <c r="C878" s="30"/>
-      <c r="D878" s="30"/>
-      <c r="E878" s="31"/>
+      <c r="B878" s="33"/>
+      <c r="C878" s="33"/>
+      <c r="D878" s="33"/>
+      <c r="E878" s="34"/>
       <c r="F878" s="22">
         <v>6402157202</v>
       </c>
@@ -36208,26 +36226,26 @@
       <c r="I878" s="11"/>
     </row>
     <row r="879" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A879" s="42" t="s">
+      <c r="A879" s="35" t="s">
         <v>1122</v>
       </c>
-      <c r="B879" s="43"/>
-      <c r="C879" s="43"/>
-      <c r="D879" s="43"/>
-      <c r="E879" s="43"/>
-      <c r="F879" s="43"/>
-      <c r="G879" s="43"/>
-      <c r="H879" s="43"/>
-      <c r="I879" s="44"/>
+      <c r="B879" s="36"/>
+      <c r="C879" s="36"/>
+      <c r="D879" s="36"/>
+      <c r="E879" s="36"/>
+      <c r="F879" s="36"/>
+      <c r="G879" s="36"/>
+      <c r="H879" s="36"/>
+      <c r="I879" s="37"/>
     </row>
     <row r="880" spans="1:9" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A880" s="29" t="s">
+      <c r="A880" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B880" s="30"/>
-      <c r="C880" s="30"/>
-      <c r="D880" s="30"/>
-      <c r="E880" s="31"/>
+      <c r="B880" s="33"/>
+      <c r="C880" s="33"/>
+      <c r="D880" s="33"/>
+      <c r="E880" s="34"/>
       <c r="F880" s="22">
         <v>224471112</v>
       </c>
@@ -36263,13 +36281,13 @@
       </c>
     </row>
     <row r="882" spans="1:9" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A882" s="29" t="s">
+      <c r="A882" s="32" t="s">
         <v>964</v>
       </c>
-      <c r="B882" s="30"/>
-      <c r="C882" s="30"/>
-      <c r="D882" s="30"/>
-      <c r="E882" s="31"/>
+      <c r="B882" s="33"/>
+      <c r="C882" s="33"/>
+      <c r="D882" s="33"/>
+      <c r="E882" s="34"/>
       <c r="F882" s="22">
         <v>5650687</v>
       </c>
@@ -36278,13 +36296,13 @@
       <c r="I882" s="11"/>
     </row>
     <row r="883" spans="1:9" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A883" s="29" t="s">
+      <c r="A883" s="32" t="s">
         <v>965</v>
       </c>
-      <c r="B883" s="30"/>
-      <c r="C883" s="30"/>
-      <c r="D883" s="30"/>
-      <c r="E883" s="31"/>
+      <c r="B883" s="33"/>
+      <c r="C883" s="33"/>
+      <c r="D883" s="33"/>
+      <c r="E883" s="34"/>
       <c r="F883" s="22">
         <v>230121799</v>
       </c>
@@ -36293,26 +36311,26 @@
       <c r="I883" s="11"/>
     </row>
     <row r="884" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A884" s="42" t="s">
+      <c r="A884" s="35" t="s">
         <v>1125</v>
       </c>
-      <c r="B884" s="43"/>
-      <c r="C884" s="43"/>
-      <c r="D884" s="43"/>
-      <c r="E884" s="43"/>
-      <c r="F884" s="43"/>
-      <c r="G884" s="43"/>
-      <c r="H884" s="43"/>
-      <c r="I884" s="44"/>
+      <c r="B884" s="36"/>
+      <c r="C884" s="36"/>
+      <c r="D884" s="36"/>
+      <c r="E884" s="36"/>
+      <c r="F884" s="36"/>
+      <c r="G884" s="36"/>
+      <c r="H884" s="36"/>
+      <c r="I884" s="37"/>
     </row>
     <row r="885" spans="1:9" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A885" s="29" t="s">
+      <c r="A885" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B885" s="30"/>
-      <c r="C885" s="30"/>
-      <c r="D885" s="30"/>
-      <c r="E885" s="31"/>
+      <c r="B885" s="33"/>
+      <c r="C885" s="33"/>
+      <c r="D885" s="33"/>
+      <c r="E885" s="34"/>
       <c r="F885" s="22">
         <v>333381749</v>
       </c>
@@ -36348,13 +36366,13 @@
       </c>
     </row>
     <row r="887" spans="1:9" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A887" s="29" t="s">
+      <c r="A887" s="32" t="s">
         <v>964</v>
       </c>
-      <c r="B887" s="30"/>
-      <c r="C887" s="30"/>
-      <c r="D887" s="30"/>
-      <c r="E887" s="31"/>
+      <c r="B887" s="33"/>
+      <c r="C887" s="33"/>
+      <c r="D887" s="33"/>
+      <c r="E887" s="34"/>
       <c r="F887" s="22">
         <v>12789477</v>
       </c>
@@ -36363,13 +36381,13 @@
       <c r="I887" s="11"/>
     </row>
     <row r="888" spans="1:9" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A888" s="29" t="s">
+      <c r="A888" s="32" t="s">
         <v>965</v>
       </c>
-      <c r="B888" s="30"/>
-      <c r="C888" s="30"/>
-      <c r="D888" s="30"/>
-      <c r="E888" s="31"/>
+      <c r="B888" s="33"/>
+      <c r="C888" s="33"/>
+      <c r="D888" s="33"/>
+      <c r="E888" s="34"/>
       <c r="F888" s="22">
         <v>346171226</v>
       </c>
@@ -36378,26 +36396,26 @@
       <c r="I888" s="11"/>
     </row>
     <row r="889" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A889" s="42" t="s">
+      <c r="A889" s="35" t="s">
         <v>1126</v>
       </c>
-      <c r="B889" s="43"/>
-      <c r="C889" s="43"/>
-      <c r="D889" s="43"/>
-      <c r="E889" s="43"/>
-      <c r="F889" s="43"/>
-      <c r="G889" s="43"/>
-      <c r="H889" s="43"/>
-      <c r="I889" s="44"/>
+      <c r="B889" s="36"/>
+      <c r="C889" s="36"/>
+      <c r="D889" s="36"/>
+      <c r="E889" s="36"/>
+      <c r="F889" s="36"/>
+      <c r="G889" s="36"/>
+      <c r="H889" s="36"/>
+      <c r="I889" s="37"/>
     </row>
     <row r="890" spans="1:9" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A890" s="29" t="s">
+      <c r="A890" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B890" s="30"/>
-      <c r="C890" s="30"/>
-      <c r="D890" s="30"/>
-      <c r="E890" s="31"/>
+      <c r="B890" s="33"/>
+      <c r="C890" s="33"/>
+      <c r="D890" s="33"/>
+      <c r="E890" s="34"/>
       <c r="F890" s="22">
         <v>94235006</v>
       </c>
@@ -36433,13 +36451,13 @@
       </c>
     </row>
     <row r="892" spans="1:9" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A892" s="29" t="s">
+      <c r="A892" s="32" t="s">
         <v>964</v>
       </c>
-      <c r="B892" s="30"/>
-      <c r="C892" s="30"/>
-      <c r="D892" s="30"/>
-      <c r="E892" s="31"/>
+      <c r="B892" s="33"/>
+      <c r="C892" s="33"/>
+      <c r="D892" s="33"/>
+      <c r="E892" s="34"/>
       <c r="F892" s="22">
         <v>6574975</v>
       </c>
@@ -36448,13 +36466,13 @@
       <c r="I892" s="11"/>
     </row>
     <row r="893" spans="1:9" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A893" s="29" t="s">
+      <c r="A893" s="32" t="s">
         <v>965</v>
       </c>
-      <c r="B893" s="30"/>
-      <c r="C893" s="30"/>
-      <c r="D893" s="30"/>
-      <c r="E893" s="31"/>
+      <c r="B893" s="33"/>
+      <c r="C893" s="33"/>
+      <c r="D893" s="33"/>
+      <c r="E893" s="34"/>
       <c r="F893" s="22">
         <v>100809981</v>
       </c>
@@ -36463,26 +36481,26 @@
       <c r="I893" s="11"/>
     </row>
     <row r="894" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A894" s="42" t="s">
+      <c r="A894" s="35" t="s">
         <v>1127</v>
       </c>
-      <c r="B894" s="43"/>
-      <c r="C894" s="43"/>
-      <c r="D894" s="43"/>
-      <c r="E894" s="43"/>
-      <c r="F894" s="43"/>
-      <c r="G894" s="43"/>
-      <c r="H894" s="43"/>
-      <c r="I894" s="44"/>
+      <c r="B894" s="36"/>
+      <c r="C894" s="36"/>
+      <c r="D894" s="36"/>
+      <c r="E894" s="36"/>
+      <c r="F894" s="36"/>
+      <c r="G894" s="36"/>
+      <c r="H894" s="36"/>
+      <c r="I894" s="37"/>
     </row>
     <row r="895" spans="1:9" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A895" s="29" t="s">
+      <c r="A895" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B895" s="30"/>
-      <c r="C895" s="30"/>
-      <c r="D895" s="30"/>
-      <c r="E895" s="31"/>
+      <c r="B895" s="33"/>
+      <c r="C895" s="33"/>
+      <c r="D895" s="33"/>
+      <c r="E895" s="34"/>
       <c r="F895" s="23"/>
       <c r="G895" s="22">
         <v>2833026200</v>
@@ -36570,13 +36588,13 @@
       </c>
     </row>
     <row r="899" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A899" s="29" t="s">
+      <c r="A899" s="32" t="s">
         <v>964</v>
       </c>
-      <c r="B899" s="30"/>
-      <c r="C899" s="30"/>
-      <c r="D899" s="30"/>
-      <c r="E899" s="31"/>
+      <c r="B899" s="33"/>
+      <c r="C899" s="33"/>
+      <c r="D899" s="33"/>
+      <c r="E899" s="34"/>
       <c r="F899" s="22">
         <v>31649</v>
       </c>
@@ -36587,13 +36605,13 @@
       <c r="I899" s="11"/>
     </row>
     <row r="900" spans="1:9" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A900" s="29" t="s">
+      <c r="A900" s="32" t="s">
         <v>965</v>
       </c>
-      <c r="B900" s="30"/>
-      <c r="C900" s="30"/>
-      <c r="D900" s="30"/>
-      <c r="E900" s="31"/>
+      <c r="B900" s="33"/>
+      <c r="C900" s="33"/>
+      <c r="D900" s="33"/>
+      <c r="E900" s="34"/>
       <c r="F900" s="23"/>
       <c r="G900" s="22">
         <v>2835508929</v>
@@ -36602,26 +36620,26 @@
       <c r="I900" s="11"/>
     </row>
     <row r="901" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A901" s="42" t="s">
+      <c r="A901" s="35" t="s">
         <v>1129</v>
       </c>
-      <c r="B901" s="43"/>
-      <c r="C901" s="43"/>
-      <c r="D901" s="43"/>
-      <c r="E901" s="43"/>
-      <c r="F901" s="43"/>
-      <c r="G901" s="43"/>
-      <c r="H901" s="43"/>
-      <c r="I901" s="44"/>
+      <c r="B901" s="36"/>
+      <c r="C901" s="36"/>
+      <c r="D901" s="36"/>
+      <c r="E901" s="36"/>
+      <c r="F901" s="36"/>
+      <c r="G901" s="36"/>
+      <c r="H901" s="36"/>
+      <c r="I901" s="37"/>
     </row>
     <row r="902" spans="1:9" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A902" s="29" t="s">
+      <c r="A902" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B902" s="30"/>
-      <c r="C902" s="30"/>
-      <c r="D902" s="30"/>
-      <c r="E902" s="31"/>
+      <c r="B902" s="33"/>
+      <c r="C902" s="33"/>
+      <c r="D902" s="33"/>
+      <c r="E902" s="34"/>
       <c r="F902" s="22">
         <v>35669605405</v>
       </c>
@@ -36630,26 +36648,26 @@
       <c r="I902" s="11"/>
     </row>
     <row r="903" spans="1:9" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A903" s="29" t="s">
+      <c r="A903" s="32" t="s">
         <v>964</v>
       </c>
-      <c r="B903" s="30"/>
-      <c r="C903" s="30"/>
-      <c r="D903" s="30"/>
-      <c r="E903" s="31"/>
+      <c r="B903" s="33"/>
+      <c r="C903" s="33"/>
+      <c r="D903" s="33"/>
+      <c r="E903" s="34"/>
       <c r="F903" s="23"/>
       <c r="G903" s="23"/>
       <c r="H903" s="10"/>
       <c r="I903" s="11"/>
     </row>
     <row r="904" spans="1:9" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A904" s="29" t="s">
+      <c r="A904" s="32" t="s">
         <v>965</v>
       </c>
-      <c r="B904" s="30"/>
-      <c r="C904" s="30"/>
-      <c r="D904" s="30"/>
-      <c r="E904" s="31"/>
+      <c r="B904" s="33"/>
+      <c r="C904" s="33"/>
+      <c r="D904" s="33"/>
+      <c r="E904" s="34"/>
       <c r="F904" s="22">
         <v>35669605405</v>
       </c>
@@ -36658,26 +36676,26 @@
       <c r="I904" s="11"/>
     </row>
     <row r="905" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A905" s="42" t="s">
+      <c r="A905" s="35" t="s">
         <v>1130</v>
       </c>
-      <c r="B905" s="43"/>
-      <c r="C905" s="43"/>
-      <c r="D905" s="43"/>
-      <c r="E905" s="43"/>
-      <c r="F905" s="43"/>
-      <c r="G905" s="43"/>
-      <c r="H905" s="43"/>
-      <c r="I905" s="44"/>
+      <c r="B905" s="36"/>
+      <c r="C905" s="36"/>
+      <c r="D905" s="36"/>
+      <c r="E905" s="36"/>
+      <c r="F905" s="36"/>
+      <c r="G905" s="36"/>
+      <c r="H905" s="36"/>
+      <c r="I905" s="37"/>
     </row>
     <row r="906" spans="1:9" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A906" s="29" t="s">
+      <c r="A906" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B906" s="30"/>
-      <c r="C906" s="30"/>
-      <c r="D906" s="30"/>
-      <c r="E906" s="31"/>
+      <c r="B906" s="33"/>
+      <c r="C906" s="33"/>
+      <c r="D906" s="33"/>
+      <c r="E906" s="34"/>
       <c r="F906" s="23"/>
       <c r="G906" s="23"/>
       <c r="H906" s="10"/>
@@ -36738,13 +36756,13 @@
       </c>
     </row>
     <row r="909" spans="1:9" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A909" s="29" t="s">
+      <c r="A909" s="32" t="s">
         <v>964</v>
       </c>
-      <c r="B909" s="30"/>
-      <c r="C909" s="30"/>
-      <c r="D909" s="30"/>
-      <c r="E909" s="31"/>
+      <c r="B909" s="33"/>
+      <c r="C909" s="33"/>
+      <c r="D909" s="33"/>
+      <c r="E909" s="34"/>
       <c r="F909" s="23"/>
       <c r="G909" s="22">
         <v>9821257247</v>
@@ -36753,13 +36771,13 @@
       <c r="I909" s="11"/>
     </row>
     <row r="910" spans="1:9" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A910" s="29" t="s">
+      <c r="A910" s="32" t="s">
         <v>965</v>
       </c>
-      <c r="B910" s="30"/>
-      <c r="C910" s="30"/>
-      <c r="D910" s="30"/>
-      <c r="E910" s="31"/>
+      <c r="B910" s="33"/>
+      <c r="C910" s="33"/>
+      <c r="D910" s="33"/>
+      <c r="E910" s="34"/>
       <c r="F910" s="23"/>
       <c r="G910" s="22">
         <v>9821257247</v>
@@ -36768,26 +36786,26 @@
       <c r="I910" s="11"/>
     </row>
     <row r="911" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A911" s="42" t="s">
+      <c r="A911" s="35" t="s">
         <v>1136</v>
       </c>
-      <c r="B911" s="43"/>
-      <c r="C911" s="43"/>
-      <c r="D911" s="43"/>
-      <c r="E911" s="43"/>
-      <c r="F911" s="43"/>
-      <c r="G911" s="43"/>
-      <c r="H911" s="43"/>
-      <c r="I911" s="44"/>
+      <c r="B911" s="36"/>
+      <c r="C911" s="36"/>
+      <c r="D911" s="36"/>
+      <c r="E911" s="36"/>
+      <c r="F911" s="36"/>
+      <c r="G911" s="36"/>
+      <c r="H911" s="36"/>
+      <c r="I911" s="37"/>
     </row>
     <row r="912" spans="1:9" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A912" s="29" t="s">
+      <c r="A912" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B912" s="30"/>
-      <c r="C912" s="30"/>
-      <c r="D912" s="30"/>
-      <c r="E912" s="31"/>
+      <c r="B912" s="33"/>
+      <c r="C912" s="33"/>
+      <c r="D912" s="33"/>
+      <c r="E912" s="34"/>
       <c r="F912" s="23"/>
       <c r="G912" s="22">
         <v>2522257803</v>
@@ -36823,13 +36841,13 @@
       </c>
     </row>
     <row r="914" spans="1:9" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A914" s="29" t="s">
+      <c r="A914" s="32" t="s">
         <v>964</v>
       </c>
-      <c r="B914" s="30"/>
-      <c r="C914" s="30"/>
-      <c r="D914" s="30"/>
-      <c r="E914" s="31"/>
+      <c r="B914" s="33"/>
+      <c r="C914" s="33"/>
+      <c r="D914" s="33"/>
+      <c r="E914" s="34"/>
       <c r="F914" s="22">
         <v>2146794974</v>
       </c>
@@ -36838,13 +36856,13 @@
       <c r="I914" s="11"/>
     </row>
     <row r="915" spans="1:9" ht="22.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A915" s="29" t="s">
+      <c r="A915" s="32" t="s">
         <v>965</v>
       </c>
-      <c r="B915" s="30"/>
-      <c r="C915" s="30"/>
-      <c r="D915" s="30"/>
-      <c r="E915" s="31"/>
+      <c r="B915" s="33"/>
+      <c r="C915" s="33"/>
+      <c r="D915" s="33"/>
+      <c r="E915" s="34"/>
       <c r="F915" s="23"/>
       <c r="G915" s="22">
         <v>375462829</v>
@@ -36888,8 +36906,8 @@
       <c r="E918" s="10"/>
     </row>
     <row r="919" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A919" s="45"/>
-      <c r="B919" s="45"/>
+      <c r="A919" s="31"/>
+      <c r="B919" s="31"/>
       <c r="C919" s="17" t="s">
         <v>1144</v>
       </c>
@@ -36925,61 +36943,14 @@
     <sortCondition ref="I842:I860"/>
   </sortState>
   <mergeCells count="79">
-    <mergeCell ref="A919:B919"/>
-    <mergeCell ref="A909:E909"/>
-    <mergeCell ref="A910:E910"/>
-    <mergeCell ref="A911:I911"/>
-    <mergeCell ref="A912:E912"/>
-    <mergeCell ref="A914:E914"/>
-    <mergeCell ref="A915:E915"/>
-    <mergeCell ref="A906:E906"/>
-    <mergeCell ref="A892:E892"/>
-    <mergeCell ref="A893:E893"/>
-    <mergeCell ref="A894:I894"/>
-    <mergeCell ref="A895:E895"/>
-    <mergeCell ref="A899:E899"/>
-    <mergeCell ref="A900:E900"/>
-    <mergeCell ref="A901:I901"/>
-    <mergeCell ref="A902:E902"/>
-    <mergeCell ref="A903:E903"/>
-    <mergeCell ref="A904:E904"/>
-    <mergeCell ref="A905:I905"/>
-    <mergeCell ref="A890:E890"/>
-    <mergeCell ref="A877:E877"/>
-    <mergeCell ref="A878:E878"/>
-    <mergeCell ref="A879:I879"/>
-    <mergeCell ref="A880:E880"/>
-    <mergeCell ref="A882:E882"/>
-    <mergeCell ref="A883:E883"/>
-    <mergeCell ref="A884:I884"/>
-    <mergeCell ref="A885:E885"/>
-    <mergeCell ref="A887:E887"/>
-    <mergeCell ref="A888:E888"/>
-    <mergeCell ref="A889:I889"/>
-    <mergeCell ref="A870:E870"/>
-    <mergeCell ref="A838:E838"/>
-    <mergeCell ref="A839:E839"/>
-    <mergeCell ref="A840:I840"/>
-    <mergeCell ref="A841:E841"/>
-    <mergeCell ref="A861:E861"/>
-    <mergeCell ref="A862:E862"/>
-    <mergeCell ref="A863:I863"/>
-    <mergeCell ref="A864:E864"/>
-    <mergeCell ref="A867:E867"/>
-    <mergeCell ref="A868:E868"/>
-    <mergeCell ref="A869:I869"/>
-    <mergeCell ref="A835:E835"/>
-    <mergeCell ref="A823:E823"/>
-    <mergeCell ref="A824:E824"/>
-    <mergeCell ref="A825:I825"/>
-    <mergeCell ref="A826:E826"/>
-    <mergeCell ref="A828:E828"/>
-    <mergeCell ref="A829:E829"/>
-    <mergeCell ref="A830:I830"/>
-    <mergeCell ref="A831:E831"/>
-    <mergeCell ref="A832:E832"/>
-    <mergeCell ref="A833:E833"/>
-    <mergeCell ref="A834:I834"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="E9:E10"/>
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="G9:G10"/>
     <mergeCell ref="H9:H10"/>
@@ -36996,14 +36967,61 @@
     <mergeCell ref="A809:E809"/>
     <mergeCell ref="A810:E810"/>
     <mergeCell ref="A811:I811"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="A835:E835"/>
+    <mergeCell ref="A823:E823"/>
+    <mergeCell ref="A824:E824"/>
+    <mergeCell ref="A825:I825"/>
+    <mergeCell ref="A826:E826"/>
+    <mergeCell ref="A828:E828"/>
+    <mergeCell ref="A829:E829"/>
+    <mergeCell ref="A830:I830"/>
+    <mergeCell ref="A831:E831"/>
+    <mergeCell ref="A832:E832"/>
+    <mergeCell ref="A833:E833"/>
+    <mergeCell ref="A834:I834"/>
+    <mergeCell ref="A870:E870"/>
+    <mergeCell ref="A838:E838"/>
+    <mergeCell ref="A839:E839"/>
+    <mergeCell ref="A840:I840"/>
+    <mergeCell ref="A841:E841"/>
+    <mergeCell ref="A861:E861"/>
+    <mergeCell ref="A862:E862"/>
+    <mergeCell ref="A863:I863"/>
+    <mergeCell ref="A864:E864"/>
+    <mergeCell ref="A867:E867"/>
+    <mergeCell ref="A868:E868"/>
+    <mergeCell ref="A869:I869"/>
+    <mergeCell ref="A890:E890"/>
+    <mergeCell ref="A877:E877"/>
+    <mergeCell ref="A878:E878"/>
+    <mergeCell ref="A879:I879"/>
+    <mergeCell ref="A880:E880"/>
+    <mergeCell ref="A882:E882"/>
+    <mergeCell ref="A883:E883"/>
+    <mergeCell ref="A884:I884"/>
+    <mergeCell ref="A885:E885"/>
+    <mergeCell ref="A887:E887"/>
+    <mergeCell ref="A888:E888"/>
+    <mergeCell ref="A889:I889"/>
+    <mergeCell ref="A906:E906"/>
+    <mergeCell ref="A892:E892"/>
+    <mergeCell ref="A893:E893"/>
+    <mergeCell ref="A894:I894"/>
+    <mergeCell ref="A895:E895"/>
+    <mergeCell ref="A899:E899"/>
+    <mergeCell ref="A900:E900"/>
+    <mergeCell ref="A901:I901"/>
+    <mergeCell ref="A902:E902"/>
+    <mergeCell ref="A903:E903"/>
+    <mergeCell ref="A904:E904"/>
+    <mergeCell ref="A905:I905"/>
+    <mergeCell ref="A919:B919"/>
+    <mergeCell ref="A909:E909"/>
+    <mergeCell ref="A910:E910"/>
+    <mergeCell ref="A911:I911"/>
+    <mergeCell ref="A912:E912"/>
+    <mergeCell ref="A914:E914"/>
+    <mergeCell ref="A915:E915"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
